--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_27_42.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_27_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1932519.074079821</v>
+        <v>1932577.358656645</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8261718.215717362</v>
+        <v>8259463.104317956</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11300164.78834108</v>
+        <v>11305628.77368751</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5361668.666736893</v>
+        <v>5361399.59402548</v>
       </c>
     </row>
     <row r="11">
@@ -8667,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>159.0459045266863</v>
+        <v>161.9098085356011</v>
       </c>
       <c r="K11" t="n">
         <v>220.0898510449805</v>
@@ -8688,7 +8688,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
-        <v>200.3056898744495</v>
+        <v>200.0361980485666</v>
       </c>
       <c r="R11" t="n">
         <v>65.71641987298243</v>
@@ -8746,19 +8746,19 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>104.8376266666667</v>
+        <v>104.5681348407838</v>
       </c>
       <c r="K12" t="n">
         <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>116.2848879539913</v>
       </c>
       <c r="M12" t="n">
-        <v>125.9453546767353</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>109.3417120833333</v>
+        <v>109.0722202574505</v>
       </c>
       <c r="O12" t="n">
         <v>142.5962444444444</v>
@@ -8831,19 +8831,19 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>112.8846762812383</v>
+        <v>112.6151844553554</v>
       </c>
       <c r="M13" t="n">
-        <v>116.9257839476051</v>
+        <v>116.6562921217222</v>
       </c>
       <c r="N13" t="n">
-        <v>105.6855444652332</v>
+        <v>105.4160526393503</v>
       </c>
       <c r="O13" t="n">
-        <v>116.4565384518428</v>
+        <v>116.1870466259599</v>
       </c>
       <c r="P13" t="n">
-        <v>115.7280040491476</v>
+        <v>115.4585122232648</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>87.04590452668629</v>
+        <v>86.60971554679898</v>
       </c>
       <c r="K14" t="n">
         <v>220.0898510449805</v>
@@ -8925,7 +8925,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
-        <v>128.3056898744495</v>
+        <v>127.8695008945622</v>
       </c>
       <c r="R14" t="n">
         <v>65.71641987298243</v>
@@ -8980,10 +8980,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10.12574714858493</v>
+        <v>5.086191020112693</v>
       </c>
       <c r="J15" t="n">
-        <v>53.06444819732754</v>
+        <v>32.40143768677939</v>
       </c>
       <c r="K15" t="n">
         <v>137.841438974359</v>
@@ -8992,16 +8992,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>48.13403392201832</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>142.5962444444444</v>
+        <v>48.16005546455713</v>
       </c>
       <c r="P15" t="n">
-        <v>39.97440741433024</v>
+        <v>64.48362684422359</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9062,28 +9062,28 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>32.99542143939611</v>
+        <v>32.55923245950881</v>
       </c>
       <c r="K16" t="n">
-        <v>35.01325817053538</v>
+        <v>34.57706919064807</v>
       </c>
       <c r="L16" t="n">
-        <v>40.88467628123828</v>
+        <v>40.44848730135098</v>
       </c>
       <c r="M16" t="n">
-        <v>44.92578394760505</v>
+        <v>44.48959496771775</v>
       </c>
       <c r="N16" t="n">
-        <v>33.68554446523319</v>
+        <v>33.24935548534589</v>
       </c>
       <c r="O16" t="n">
-        <v>44.45653845184279</v>
+        <v>44.02034947195548</v>
       </c>
       <c r="P16" t="n">
-        <v>43.72800404914761</v>
+        <v>43.29181506926031</v>
       </c>
       <c r="Q16" t="n">
-        <v>57.50500162944584</v>
+        <v>57.06881264955854</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>87.04590452668629</v>
+        <v>86.60971554679898</v>
       </c>
       <c r="K17" t="n">
         <v>220.0898510449805</v>
@@ -9162,7 +9162,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
-        <v>128.3056898744495</v>
+        <v>127.8695008945622</v>
       </c>
       <c r="R17" t="n">
         <v>65.71641987298243</v>
@@ -9217,13 +9217,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5.522379999999998</v>
+        <v>5.086191020112693</v>
       </c>
       <c r="J18" t="n">
-        <v>32.83762666666669</v>
+        <v>32.40143768677939</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>68.35065840425288</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
@@ -9232,16 +9232,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N18" t="n">
-        <v>62.17190076257859</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>39.53821843444294</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.98177408602152</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9299,28 +9299,28 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>32.99542143939611</v>
+        <v>32.55923245950881</v>
       </c>
       <c r="K19" t="n">
-        <v>35.01325817053538</v>
+        <v>34.57706919064807</v>
       </c>
       <c r="L19" t="n">
-        <v>40.88467628123828</v>
+        <v>40.44848730135098</v>
       </c>
       <c r="M19" t="n">
-        <v>44.92578394760505</v>
+        <v>44.48959496771775</v>
       </c>
       <c r="N19" t="n">
-        <v>33.68554446523319</v>
+        <v>33.24935548534589</v>
       </c>
       <c r="O19" t="n">
-        <v>44.45653845184279</v>
+        <v>44.02034947195548</v>
       </c>
       <c r="P19" t="n">
-        <v>43.72800404914761</v>
+        <v>43.29181506926031</v>
       </c>
       <c r="Q19" t="n">
-        <v>57.50500162944584</v>
+        <v>57.06881264955854</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>87.04590452668629</v>
+        <v>86.60971554679898</v>
       </c>
       <c r="K20" t="n">
         <v>220.0898510449805</v>
@@ -9399,7 +9399,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
-        <v>128.3056898744495</v>
+        <v>127.8695008945622</v>
       </c>
       <c r="R20" t="n">
         <v>65.71641987298243</v>
@@ -9454,10 +9454,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>5.522379999999998</v>
+        <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>32.83762666666669</v>
+        <v>32.40143768677939</v>
       </c>
       <c r="K21" t="n">
         <v>137.841438974359</v>
@@ -9466,19 +9466,19 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>48.13403392201832</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>36.905523103446</v>
       </c>
       <c r="O21" t="n">
-        <v>73.42643312368972</v>
+        <v>48.16005546455713</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>39.53821843444294</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>45.54558510613421</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9536,28 +9536,28 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>32.99542143939611</v>
+        <v>32.55923245950881</v>
       </c>
       <c r="K22" t="n">
-        <v>35.01325817053538</v>
+        <v>34.57706919064807</v>
       </c>
       <c r="L22" t="n">
-        <v>40.88467628123828</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M22" t="n">
-        <v>44.92578394760505</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N22" t="n">
-        <v>33.68554446523319</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O22" t="n">
-        <v>44.45653845184279</v>
+        <v>44.02034947195548</v>
       </c>
       <c r="P22" t="n">
-        <v>43.72800404914761</v>
+        <v>128.8247882221783</v>
       </c>
       <c r="Q22" t="n">
-        <v>57.50500162944584</v>
+        <v>57.06881264955854</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>87.04590452668629</v>
+        <v>86.60971554679898</v>
       </c>
       <c r="K23" t="n">
         <v>220.0898510449805</v>
@@ -9636,7 +9636,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q23" t="n">
-        <v>141.5318205277158</v>
+        <v>127.8695008945622</v>
       </c>
       <c r="R23" t="n">
         <v>65.71641987298243</v>
@@ -9691,13 +9691,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5.522379999999998</v>
+        <v>5.086191020112693</v>
       </c>
       <c r="J24" t="n">
-        <v>32.83762666666669</v>
+        <v>32.40143768677939</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>43.40524999447169</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -9706,16 +9706,16 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>37.34171208333331</v>
+        <v>36.905523103446</v>
       </c>
       <c r="O24" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
-        <v>39.97440741433024</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>45.54558510613421</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9773,28 +9773,28 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>32.99542143939611</v>
+        <v>32.55923245950881</v>
       </c>
       <c r="K25" t="n">
-        <v>35.01325817053538</v>
+        <v>34.57706919064807</v>
       </c>
       <c r="L25" t="n">
-        <v>40.88467628123828</v>
+        <v>40.44848730135098</v>
       </c>
       <c r="M25" t="n">
-        <v>44.92578394760505</v>
+        <v>60.97200073660264</v>
       </c>
       <c r="N25" t="n">
-        <v>33.68554446523319</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O25" t="n">
-        <v>44.45653845184279</v>
+        <v>44.02034947195548</v>
       </c>
       <c r="P25" t="n">
-        <v>43.72800404914761</v>
+        <v>135.0065633140411</v>
       </c>
       <c r="Q25" t="n">
-        <v>57.50500162944584</v>
+        <v>65.34295837775146</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>91.04590452668629</v>
+        <v>104.2276923779817</v>
       </c>
       <c r="K26" t="n">
         <v>220.0898510449805</v>
@@ -9873,7 +9873,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q26" t="n">
-        <v>144.6476149108817</v>
+        <v>132.9090570230344</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,13 +9931,13 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>36.83762666666669</v>
+        <v>37.44099381525162</v>
       </c>
       <c r="K27" t="n">
-        <v>137.841438974359</v>
+        <v>48.44480612294392</v>
       </c>
       <c r="L27" t="n">
-        <v>48.55437977987418</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
@@ -9949,10 +9949,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>43.97440741433024</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>50.58514123460644</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,25 +10013,25 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>39.01325817053538</v>
+        <v>39.6166253191203</v>
       </c>
       <c r="L28" t="n">
-        <v>44.88467628123828</v>
+        <v>45.48804342982321</v>
       </c>
       <c r="M28" t="n">
-        <v>48.92578394760505</v>
+        <v>49.52915109618998</v>
       </c>
       <c r="N28" t="n">
-        <v>37.68554446523319</v>
+        <v>38.28891161381812</v>
       </c>
       <c r="O28" t="n">
-        <v>48.45653845184279</v>
+        <v>49.05990560042771</v>
       </c>
       <c r="P28" t="n">
-        <v>47.72800404914761</v>
+        <v>48.33137119773254</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.50500162944584</v>
+        <v>62.10836877803077</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>43.04590452668629</v>
+        <v>43.70238736347562</v>
       </c>
       <c r="K29" t="n">
         <v>220.0898510449805</v>
@@ -10110,7 +10110,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
-        <v>84.30568987444948</v>
+        <v>84.96217271123882</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10171,25 +10171,25 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.4979218111483306</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5543797798741821</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>4.134033922018318</v>
+        <v>8.572342566367553</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4.596244444444437</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>2.638256922810854</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10247,28 +10247,28 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>10.26460111459834</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>134.8846762812383</v>
       </c>
       <c r="M31" t="n">
-        <v>138.9257839476051</v>
+        <v>1.582266784394392</v>
       </c>
       <c r="N31" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>138.4565384518428</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.3844868859369512</v>
       </c>
       <c r="Q31" t="n">
-        <v>13.50500162944584</v>
+        <v>14.16148446623518</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>43.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K32" t="n">
         <v>220.0898510449805</v>
@@ -10347,7 +10347,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
-        <v>84.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R32" t="n">
         <v>65.71641987298243</v>
@@ -10408,10 +10408,10 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.497921811148359</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5543797798741821</v>
+        <v>1.210862616663547</v>
       </c>
       <c r="M33" t="n">
         <v>142.1340339220183</v>
@@ -10420,16 +10420,16 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4.596244444444437</v>
+        <v>52.58668516499515</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>2.638256922810882</v>
       </c>
       <c r="R33" t="n">
-        <v>45.52166981132082</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -10502,10 +10502,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q34" t="n">
-        <v>16.65772250936055</v>
+        <v>14.16148446623521</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>43.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K35" t="n">
         <v>220.0898510449805</v>
@@ -10584,7 +10584,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
-        <v>84.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10639,34 +10639,34 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>10.12574714858493</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.497921811148359</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5543797798741821</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>142.1340339220183</v>
+        <v>129.866088131178</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.596244444444437</v>
+        <v>5.252727281233803</v>
       </c>
       <c r="P36" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.981774086021517</v>
+        <v>2.638256922810882</v>
       </c>
       <c r="R36" t="n">
-        <v>41.2060742370374</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -10736,13 +10736,13 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O37" t="n">
-        <v>138.4565384518428</v>
+        <v>1.113021288632154</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q37" t="n">
-        <v>13.50500162944584</v>
+        <v>14.16148446623521</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>43.04590452668629</v>
+        <v>43.70238736347565</v>
       </c>
       <c r="K38" t="n">
         <v>220.0898510449805</v>
@@ -10821,7 +10821,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
-        <v>84.30568987444948</v>
+        <v>84.96217271123885</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10882,28 +10882,28 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>120.8125867089954</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5543797798741821</v>
+        <v>1.210862616663547</v>
       </c>
       <c r="M39" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.596244444444437</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.42462099131993</v>
+        <v>2.638256922810882</v>
       </c>
       <c r="R39" t="n">
-        <v>45.52166981132082</v>
+        <v>8.335986800753318</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -10964,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>138.9257839476051</v>
@@ -10976,10 +10976,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.3844868859369797</v>
       </c>
       <c r="Q40" t="n">
-        <v>13.50500162944584</v>
+        <v>14.16148446623521</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -11037,7 +11037,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>61.04590452668629</v>
+        <v>60.93232306088625</v>
       </c>
       <c r="K41" t="n">
         <v>220.0898510449805</v>
@@ -11058,7 +11058,7 @@
         <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
-        <v>135.2189089272072</v>
+        <v>102.1921084086494</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11113,34 +11113,34 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>10.12574714858493</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>6.837626666666694</v>
+        <v>6.724045200866655</v>
       </c>
       <c r="K42" t="n">
-        <v>17.84143897435899</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>138.5543797798742</v>
+        <v>18.44079831407414</v>
       </c>
       <c r="M42" t="n">
-        <v>22.13403392201832</v>
+        <v>22.02045245621828</v>
       </c>
       <c r="N42" t="n">
-        <v>11.34171208333331</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>22.4826629786444</v>
       </c>
       <c r="P42" t="n">
-        <v>13.97440741433024</v>
+        <v>13.86082594853021</v>
       </c>
       <c r="Q42" t="n">
-        <v>19.98177408602152</v>
+        <v>111.5124353909146</v>
       </c>
       <c r="R42" t="n">
-        <v>45.52166981132082</v>
+        <v>25.56592249816391</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -11195,10 +11195,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>6.995421439396111</v>
+        <v>6.881839973596072</v>
       </c>
       <c r="K43" t="n">
-        <v>9.01325817053538</v>
+        <v>8.899676704735342</v>
       </c>
       <c r="L43" t="n">
         <v>134.8846762812383</v>
@@ -11213,10 +11213,10 @@
         <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
-        <v>17.72800404914761</v>
+        <v>17.61442258334758</v>
       </c>
       <c r="Q43" t="n">
-        <v>31.50500162944584</v>
+        <v>31.3914201636458</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>360.7338416634806</v>
+        <v>360.4643498375978</v>
       </c>
       <c r="C11" t="n">
-        <v>343.2728917710076</v>
+        <v>343.0033999451247</v>
       </c>
       <c r="D11" t="n">
-        <v>332.683041620683</v>
+        <v>332.4135497948001</v>
       </c>
       <c r="E11" t="n">
-        <v>359.9303700722618</v>
+        <v>359.660878246379</v>
       </c>
       <c r="F11" t="n">
-        <v>384.8760457417114</v>
+        <v>384.6065539158286</v>
       </c>
       <c r="G11" t="n">
-        <v>393.302737515135</v>
+        <v>393.0332456892522</v>
       </c>
       <c r="H11" t="n">
-        <v>317.4748021157671</v>
+        <v>317.2053102898843</v>
       </c>
       <c r="I11" t="n">
-        <v>188.4758895704059</v>
+        <v>188.2063977445231</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>127.8691179411497</v>
+        <v>127.5996261152668</v>
       </c>
       <c r="S11" t="n">
-        <v>187.0200695862453</v>
+        <v>186.7505777603625</v>
       </c>
       <c r="T11" t="n">
-        <v>201.0958495641314</v>
+        <v>200.8263577382485</v>
       </c>
       <c r="U11" t="n">
-        <v>229.3456529078365</v>
+        <v>229.0761610819536</v>
       </c>
       <c r="V11" t="n">
-        <v>305.7522584701349</v>
+        <v>305.482766644252</v>
       </c>
       <c r="W11" t="n">
-        <v>327.240968717413</v>
+        <v>326.9714768915302</v>
       </c>
       <c r="X11" t="n">
-        <v>347.731100678469</v>
+        <v>347.4616088525862</v>
       </c>
       <c r="Y11" t="n">
-        <v>364.2379386560536</v>
+        <v>363.9684468301707</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144.5331836498673</v>
+        <v>144.2636918239845</v>
       </c>
       <c r="C12" t="n">
-        <v>150.7084989883157</v>
+        <v>150.4390071624329</v>
       </c>
       <c r="D12" t="n">
-        <v>125.4450655646388</v>
+        <v>125.1755737387559</v>
       </c>
       <c r="E12" t="n">
-        <v>135.6450804554009</v>
+        <v>135.3755886295181</v>
       </c>
       <c r="F12" t="n">
-        <v>123.0692123933839</v>
+        <v>122.799720567501</v>
       </c>
       <c r="G12" t="n">
-        <v>115.3435171632106</v>
+        <v>115.0740253373278</v>
       </c>
       <c r="H12" t="n">
-        <v>90.23544423649646</v>
+        <v>89.96595241061361</v>
       </c>
       <c r="I12" t="n">
-        <v>67.39663285141508</v>
+        <v>67.12714102553223</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.15783415264313</v>
+        <v>77.88834232676028</v>
       </c>
       <c r="S12" t="n">
-        <v>149.6831711038378</v>
+        <v>149.413679277955</v>
       </c>
       <c r="T12" t="n">
-        <v>178.1647286948216</v>
+        <v>177.8952368689388</v>
       </c>
       <c r="U12" t="n">
-        <v>203.9413820809748</v>
+        <v>203.671890255092</v>
       </c>
       <c r="V12" t="n">
-        <v>210.8005871494253</v>
+        <v>210.5310953235424</v>
       </c>
       <c r="W12" t="n">
-        <v>229.6949831609196</v>
+        <v>229.4254913350368</v>
       </c>
       <c r="X12" t="n">
-        <v>183.7729852034775</v>
+        <v>183.5034933775946</v>
       </c>
       <c r="Y12" t="n">
-        <v>183.6826957773044</v>
+        <v>183.4132039514215</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>157.8319801819373</v>
+        <v>157.5624883560544</v>
       </c>
       <c r="C13" t="n">
-        <v>145.2468210986278</v>
+        <v>144.977329272745</v>
       </c>
       <c r="D13" t="n">
-        <v>126.6154730182124</v>
+        <v>126.3459811923295</v>
       </c>
       <c r="E13" t="n">
-        <v>124.4339626465692</v>
+        <v>124.1644708206863</v>
       </c>
       <c r="F13" t="n">
-        <v>123.4210480229312</v>
+        <v>123.1515561970484</v>
       </c>
       <c r="G13" t="n">
-        <v>145.9909793584588</v>
+        <v>145.7214875325759</v>
       </c>
       <c r="H13" t="n">
-        <v>140.2271725074396</v>
+        <v>139.9576806815567</v>
       </c>
       <c r="I13" t="n">
-        <v>133.4504749272583</v>
+        <v>133.1809831013754</v>
       </c>
       <c r="J13" t="n">
-        <v>71.35918011667277</v>
+        <v>71.08968829078992</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2694918258828523</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>64.16204325169439</v>
+        <v>63.89255142581153</v>
       </c>
       <c r="R13" t="n">
-        <v>155.2933913771695</v>
+        <v>155.0238995512866</v>
       </c>
       <c r="S13" t="n">
-        <v>202.0165980369723</v>
+        <v>201.7471062110894</v>
       </c>
       <c r="T13" t="n">
-        <v>205.9455894282815</v>
+        <v>205.6760976023986</v>
       </c>
       <c r="U13" t="n">
-        <v>264.3190293564909</v>
+        <v>264.0495375306081</v>
       </c>
       <c r="V13" t="n">
-        <v>230.137643323828</v>
+        <v>229.8681514979451</v>
       </c>
       <c r="W13" t="n">
-        <v>264.522998336591</v>
+        <v>264.2535065107081</v>
       </c>
       <c r="X13" t="n">
-        <v>203.7096553890372</v>
+        <v>203.4401635631543</v>
       </c>
       <c r="Y13" t="n">
-        <v>196.5846533520948</v>
+        <v>196.3151615262119</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>288.7338416634806</v>
+        <v>288.2976526835932</v>
       </c>
       <c r="C14" t="n">
-        <v>271.2728917710076</v>
+        <v>270.8367027911203</v>
       </c>
       <c r="D14" t="n">
-        <v>260.683041620683</v>
+        <v>260.2468526407956</v>
       </c>
       <c r="E14" t="n">
-        <v>287.9303700722618</v>
+        <v>287.4941810923744</v>
       </c>
       <c r="F14" t="n">
-        <v>312.8760457417114</v>
+        <v>312.4398567618241</v>
       </c>
       <c r="G14" t="n">
-        <v>321.302737515135</v>
+        <v>320.8665485352477</v>
       </c>
       <c r="H14" t="n">
-        <v>245.4748021157671</v>
+        <v>245.0386131358798</v>
       </c>
       <c r="I14" t="n">
-        <v>116.4758895704059</v>
+        <v>116.0397005905186</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>55.86911794114968</v>
+        <v>55.43292896126238</v>
       </c>
       <c r="S14" t="n">
-        <v>115.0200695862453</v>
+        <v>114.583880606358</v>
       </c>
       <c r="T14" t="n">
-        <v>129.0958495641314</v>
+        <v>128.6596605842441</v>
       </c>
       <c r="U14" t="n">
-        <v>157.3456529078365</v>
+        <v>156.9094639279492</v>
       </c>
       <c r="V14" t="n">
-        <v>233.7522584701349</v>
+        <v>233.3160694902476</v>
       </c>
       <c r="W14" t="n">
-        <v>255.240968717413</v>
+        <v>254.8047797375257</v>
       </c>
       <c r="X14" t="n">
-        <v>275.731100678469</v>
+        <v>275.2949116985817</v>
       </c>
       <c r="Y14" t="n">
-        <v>292.2379386560536</v>
+        <v>291.8017496761663</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.53318364986734</v>
+        <v>72.09699466998003</v>
       </c>
       <c r="C15" t="n">
-        <v>78.70849898831574</v>
+        <v>78.27231000842843</v>
       </c>
       <c r="D15" t="n">
-        <v>53.44506556463875</v>
+        <v>53.00887658475145</v>
       </c>
       <c r="E15" t="n">
-        <v>63.64508045540094</v>
+        <v>63.20889147551364</v>
       </c>
       <c r="F15" t="n">
-        <v>51.06921239338388</v>
+        <v>50.63302341349657</v>
       </c>
       <c r="G15" t="n">
-        <v>43.34351716321063</v>
+        <v>42.90732818332333</v>
       </c>
       <c r="H15" t="n">
-        <v>18.23544423649646</v>
+        <v>17.79925525660916</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.157834152643133</v>
+        <v>5.721645172755828</v>
       </c>
       <c r="S15" t="n">
-        <v>77.68317110383782</v>
+        <v>77.24698212395052</v>
       </c>
       <c r="T15" t="n">
-        <v>106.1647286948216</v>
+        <v>105.7285397149343</v>
       </c>
       <c r="U15" t="n">
-        <v>131.9413820809748</v>
+        <v>131.5051931010875</v>
       </c>
       <c r="V15" t="n">
-        <v>138.8005871494253</v>
+        <v>138.364398169538</v>
       </c>
       <c r="W15" t="n">
-        <v>157.6949831609196</v>
+        <v>157.2587941810323</v>
       </c>
       <c r="X15" t="n">
-        <v>111.7729852034775</v>
+        <v>111.3367962235902</v>
       </c>
       <c r="Y15" t="n">
-        <v>111.6826957773044</v>
+        <v>111.2465067974171</v>
       </c>
     </row>
     <row r="16">
@@ -23610,28 +23610,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>85.8319801819373</v>
+        <v>85.39579120204999</v>
       </c>
       <c r="C16" t="n">
-        <v>73.24682109862783</v>
+        <v>72.81063211874053</v>
       </c>
       <c r="D16" t="n">
-        <v>54.61547301821236</v>
+        <v>54.17928403832505</v>
       </c>
       <c r="E16" t="n">
-        <v>52.43396264656917</v>
+        <v>51.99777366668187</v>
       </c>
       <c r="F16" t="n">
-        <v>51.42104802293125</v>
+        <v>50.98485904304394</v>
       </c>
       <c r="G16" t="n">
-        <v>73.99097935845876</v>
+        <v>73.55479037857145</v>
       </c>
       <c r="H16" t="n">
-        <v>68.22717250743958</v>
+        <v>67.79098352755227</v>
       </c>
       <c r="I16" t="n">
-        <v>61.45047492725828</v>
+        <v>61.01428594737098</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>83.29339137716948</v>
+        <v>82.85720239728218</v>
       </c>
       <c r="S16" t="n">
-        <v>130.0165980369723</v>
+        <v>129.5804090570849</v>
       </c>
       <c r="T16" t="n">
-        <v>133.9455894282815</v>
+        <v>133.5094004483942</v>
       </c>
       <c r="U16" t="n">
-        <v>192.3190293564909</v>
+        <v>191.8828403766036</v>
       </c>
       <c r="V16" t="n">
-        <v>158.137643323828</v>
+        <v>157.7014543439407</v>
       </c>
       <c r="W16" t="n">
-        <v>192.522998336591</v>
+        <v>192.0868093567037</v>
       </c>
       <c r="X16" t="n">
-        <v>131.7096553890372</v>
+        <v>131.2734664091498</v>
       </c>
       <c r="Y16" t="n">
-        <v>124.5846533520948</v>
+        <v>124.1484643722075</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>288.7338416634806</v>
+        <v>288.2976526835932</v>
       </c>
       <c r="C17" t="n">
-        <v>271.2728917710076</v>
+        <v>270.8367027911203</v>
       </c>
       <c r="D17" t="n">
-        <v>260.683041620683</v>
+        <v>260.2468526407956</v>
       </c>
       <c r="E17" t="n">
-        <v>287.9303700722618</v>
+        <v>287.4941810923744</v>
       </c>
       <c r="F17" t="n">
-        <v>312.8760457417114</v>
+        <v>312.4398567618241</v>
       </c>
       <c r="G17" t="n">
-        <v>321.302737515135</v>
+        <v>320.8665485352477</v>
       </c>
       <c r="H17" t="n">
-        <v>245.4748021157671</v>
+        <v>245.0386131358798</v>
       </c>
       <c r="I17" t="n">
-        <v>116.4758895704059</v>
+        <v>116.0397005905186</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>55.86911794114968</v>
+        <v>55.43292896126238</v>
       </c>
       <c r="S17" t="n">
-        <v>115.0200695862453</v>
+        <v>114.583880606358</v>
       </c>
       <c r="T17" t="n">
-        <v>129.0958495641314</v>
+        <v>128.6596605842441</v>
       </c>
       <c r="U17" t="n">
-        <v>157.3456529078365</v>
+        <v>156.9094639279492</v>
       </c>
       <c r="V17" t="n">
-        <v>233.7522584701349</v>
+        <v>233.3160694902476</v>
       </c>
       <c r="W17" t="n">
-        <v>255.240968717413</v>
+        <v>254.8047797375257</v>
       </c>
       <c r="X17" t="n">
-        <v>275.731100678469</v>
+        <v>275.2949116985817</v>
       </c>
       <c r="Y17" t="n">
-        <v>292.2379386560536</v>
+        <v>291.8017496761663</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>72.53318364986734</v>
+        <v>72.09699466998003</v>
       </c>
       <c r="C18" t="n">
-        <v>78.70849898831574</v>
+        <v>78.27231000842843</v>
       </c>
       <c r="D18" t="n">
-        <v>53.44506556463875</v>
+        <v>53.00887658475145</v>
       </c>
       <c r="E18" t="n">
-        <v>63.64508045540094</v>
+        <v>63.20889147551364</v>
       </c>
       <c r="F18" t="n">
-        <v>51.06921239338388</v>
+        <v>50.63302341349657</v>
       </c>
       <c r="G18" t="n">
-        <v>43.34351716321063</v>
+        <v>42.90732818332333</v>
       </c>
       <c r="H18" t="n">
-        <v>18.23544423649646</v>
+        <v>17.79925525660916</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.157834152643133</v>
+        <v>5.721645172755828</v>
       </c>
       <c r="S18" t="n">
-        <v>77.68317110383782</v>
+        <v>77.24698212395052</v>
       </c>
       <c r="T18" t="n">
-        <v>106.1647286948216</v>
+        <v>105.7285397149343</v>
       </c>
       <c r="U18" t="n">
-        <v>131.9413820809748</v>
+        <v>131.5051931010875</v>
       </c>
       <c r="V18" t="n">
-        <v>138.8005871494253</v>
+        <v>138.364398169538</v>
       </c>
       <c r="W18" t="n">
-        <v>157.6949831609196</v>
+        <v>157.2587941810323</v>
       </c>
       <c r="X18" t="n">
-        <v>111.7729852034775</v>
+        <v>111.3367962235902</v>
       </c>
       <c r="Y18" t="n">
-        <v>111.6826957773044</v>
+        <v>111.2465067974171</v>
       </c>
     </row>
     <row r="19">
@@ -23847,28 +23847,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.8319801819373</v>
+        <v>85.39579120204999</v>
       </c>
       <c r="C19" t="n">
-        <v>73.24682109862783</v>
+        <v>72.81063211874053</v>
       </c>
       <c r="D19" t="n">
-        <v>54.61547301821236</v>
+        <v>54.17928403832505</v>
       </c>
       <c r="E19" t="n">
-        <v>52.43396264656917</v>
+        <v>51.99777366668187</v>
       </c>
       <c r="F19" t="n">
-        <v>51.42104802293125</v>
+        <v>50.98485904304394</v>
       </c>
       <c r="G19" t="n">
-        <v>73.99097935845876</v>
+        <v>73.55479037857145</v>
       </c>
       <c r="H19" t="n">
-        <v>68.22717250743958</v>
+        <v>67.79098352755227</v>
       </c>
       <c r="I19" t="n">
-        <v>61.45047492725828</v>
+        <v>61.01428594737098</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>83.29339137716948</v>
+        <v>82.85720239728218</v>
       </c>
       <c r="S19" t="n">
-        <v>130.0165980369723</v>
+        <v>129.5804090570849</v>
       </c>
       <c r="T19" t="n">
-        <v>133.9455894282815</v>
+        <v>133.5094004483942</v>
       </c>
       <c r="U19" t="n">
-        <v>192.3190293564909</v>
+        <v>191.8828403766036</v>
       </c>
       <c r="V19" t="n">
-        <v>158.137643323828</v>
+        <v>157.7014543439407</v>
       </c>
       <c r="W19" t="n">
-        <v>192.522998336591</v>
+        <v>192.0868093567037</v>
       </c>
       <c r="X19" t="n">
-        <v>131.7096553890372</v>
+        <v>131.2734664091498</v>
       </c>
       <c r="Y19" t="n">
-        <v>124.5846533520948</v>
+        <v>124.1484643722075</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>288.7338416634806</v>
+        <v>288.2976526835932</v>
       </c>
       <c r="C20" t="n">
-        <v>271.2728917710076</v>
+        <v>270.8367027911203</v>
       </c>
       <c r="D20" t="n">
-        <v>260.683041620683</v>
+        <v>260.2468526407956</v>
       </c>
       <c r="E20" t="n">
-        <v>287.9303700722618</v>
+        <v>287.4941810923744</v>
       </c>
       <c r="F20" t="n">
-        <v>312.8760457417114</v>
+        <v>312.4398567618241</v>
       </c>
       <c r="G20" t="n">
-        <v>321.302737515135</v>
+        <v>320.8665485352477</v>
       </c>
       <c r="H20" t="n">
-        <v>245.4748021157671</v>
+        <v>245.0386131358798</v>
       </c>
       <c r="I20" t="n">
-        <v>116.4758895704059</v>
+        <v>116.0397005905186</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>55.86911794114968</v>
+        <v>55.43292896126238</v>
       </c>
       <c r="S20" t="n">
-        <v>115.0200695862453</v>
+        <v>114.583880606358</v>
       </c>
       <c r="T20" t="n">
-        <v>129.0958495641314</v>
+        <v>128.6596605842441</v>
       </c>
       <c r="U20" t="n">
-        <v>157.3456529078365</v>
+        <v>156.9094639279492</v>
       </c>
       <c r="V20" t="n">
-        <v>233.7522584701349</v>
+        <v>233.3160694902476</v>
       </c>
       <c r="W20" t="n">
-        <v>255.240968717413</v>
+        <v>254.8047797375257</v>
       </c>
       <c r="X20" t="n">
-        <v>275.731100678469</v>
+        <v>275.2949116985817</v>
       </c>
       <c r="Y20" t="n">
-        <v>292.2379386560536</v>
+        <v>291.8017496761663</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>72.53318364986734</v>
+        <v>72.09699466998003</v>
       </c>
       <c r="C21" t="n">
-        <v>78.70849898831574</v>
+        <v>78.27231000842843</v>
       </c>
       <c r="D21" t="n">
-        <v>53.44506556463875</v>
+        <v>53.00887658475145</v>
       </c>
       <c r="E21" t="n">
-        <v>63.64508045540094</v>
+        <v>63.20889147551364</v>
       </c>
       <c r="F21" t="n">
-        <v>51.06921239338388</v>
+        <v>50.63302341349657</v>
       </c>
       <c r="G21" t="n">
-        <v>43.34351716321063</v>
+        <v>42.90732818332333</v>
       </c>
       <c r="H21" t="n">
-        <v>18.23544423649646</v>
+        <v>17.79925525660916</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>6.157834152643133</v>
+        <v>5.721645172755828</v>
       </c>
       <c r="S21" t="n">
-        <v>77.68317110383782</v>
+        <v>77.24698212395052</v>
       </c>
       <c r="T21" t="n">
-        <v>106.1647286948216</v>
+        <v>105.7285397149343</v>
       </c>
       <c r="U21" t="n">
-        <v>131.9413820809748</v>
+        <v>131.5051931010875</v>
       </c>
       <c r="V21" t="n">
-        <v>138.8005871494253</v>
+        <v>138.364398169538</v>
       </c>
       <c r="W21" t="n">
-        <v>157.6949831609196</v>
+        <v>157.2587941810323</v>
       </c>
       <c r="X21" t="n">
-        <v>111.7729852034775</v>
+        <v>111.3367962235902</v>
       </c>
       <c r="Y21" t="n">
-        <v>111.6826957773044</v>
+        <v>111.2465067974171</v>
       </c>
     </row>
     <row r="22">
@@ -24084,28 +24084,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.8319801819373</v>
+        <v>85.39579120204999</v>
       </c>
       <c r="C22" t="n">
-        <v>73.24682109862783</v>
+        <v>72.81063211874053</v>
       </c>
       <c r="D22" t="n">
-        <v>54.61547301821236</v>
+        <v>54.17928403832505</v>
       </c>
       <c r="E22" t="n">
-        <v>52.43396264656917</v>
+        <v>51.99777366668187</v>
       </c>
       <c r="F22" t="n">
-        <v>51.42104802293125</v>
+        <v>50.98485904304394</v>
       </c>
       <c r="G22" t="n">
-        <v>73.99097935845876</v>
+        <v>73.55479037857145</v>
       </c>
       <c r="H22" t="n">
-        <v>68.22717250743958</v>
+        <v>67.79098352755227</v>
       </c>
       <c r="I22" t="n">
-        <v>61.45047492725828</v>
+        <v>61.01428594737098</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>83.29339137716948</v>
+        <v>82.85720239728218</v>
       </c>
       <c r="S22" t="n">
-        <v>130.0165980369723</v>
+        <v>129.5804090570849</v>
       </c>
       <c r="T22" t="n">
-        <v>133.9455894282815</v>
+        <v>133.5094004483942</v>
       </c>
       <c r="U22" t="n">
-        <v>192.3190293564909</v>
+        <v>191.8828403766036</v>
       </c>
       <c r="V22" t="n">
-        <v>158.137643323828</v>
+        <v>157.7014543439407</v>
       </c>
       <c r="W22" t="n">
-        <v>192.522998336591</v>
+        <v>192.0868093567037</v>
       </c>
       <c r="X22" t="n">
-        <v>131.7096553890372</v>
+        <v>131.2734664091498</v>
       </c>
       <c r="Y22" t="n">
-        <v>124.5846533520948</v>
+        <v>124.1484643722075</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>288.7338416634806</v>
+        <v>288.2976526835932</v>
       </c>
       <c r="C23" t="n">
-        <v>271.2728917710076</v>
+        <v>270.8367027911203</v>
       </c>
       <c r="D23" t="n">
-        <v>260.683041620683</v>
+        <v>260.2468526407956</v>
       </c>
       <c r="E23" t="n">
-        <v>287.9303700722618</v>
+        <v>287.4941810923744</v>
       </c>
       <c r="F23" t="n">
-        <v>312.8760457417114</v>
+        <v>312.4398567618241</v>
       </c>
       <c r="G23" t="n">
-        <v>321.302737515135</v>
+        <v>320.8665485352477</v>
       </c>
       <c r="H23" t="n">
-        <v>245.4748021157671</v>
+        <v>245.0386131358798</v>
       </c>
       <c r="I23" t="n">
-        <v>116.4758895704059</v>
+        <v>116.0397005905186</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>55.86911794114968</v>
+        <v>55.43292896126238</v>
       </c>
       <c r="S23" t="n">
-        <v>115.0200695862453</v>
+        <v>114.583880606358</v>
       </c>
       <c r="T23" t="n">
-        <v>129.0958495641314</v>
+        <v>128.6596605842441</v>
       </c>
       <c r="U23" t="n">
-        <v>157.3456529078365</v>
+        <v>156.9094639279492</v>
       </c>
       <c r="V23" t="n">
-        <v>233.7522584701349</v>
+        <v>233.3160694902476</v>
       </c>
       <c r="W23" t="n">
-        <v>255.240968717413</v>
+        <v>254.8047797375257</v>
       </c>
       <c r="X23" t="n">
-        <v>275.731100678469</v>
+        <v>275.2949116985817</v>
       </c>
       <c r="Y23" t="n">
-        <v>292.2379386560536</v>
+        <v>291.8017496761663</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>72.53318364986734</v>
+        <v>72.09699466998003</v>
       </c>
       <c r="C24" t="n">
-        <v>78.70849898831574</v>
+        <v>78.27231000842843</v>
       </c>
       <c r="D24" t="n">
-        <v>53.44506556463875</v>
+        <v>53.00887658475145</v>
       </c>
       <c r="E24" t="n">
-        <v>63.64508045540094</v>
+        <v>63.20889147551364</v>
       </c>
       <c r="F24" t="n">
-        <v>51.06921239338388</v>
+        <v>50.63302341349657</v>
       </c>
       <c r="G24" t="n">
-        <v>43.34351716321063</v>
+        <v>42.90732818332333</v>
       </c>
       <c r="H24" t="n">
-        <v>18.23544423649646</v>
+        <v>17.79925525660916</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.157834152643133</v>
+        <v>5.721645172755828</v>
       </c>
       <c r="S24" t="n">
-        <v>77.68317110383782</v>
+        <v>77.24698212395052</v>
       </c>
       <c r="T24" t="n">
-        <v>106.1647286948216</v>
+        <v>105.7285397149343</v>
       </c>
       <c r="U24" t="n">
-        <v>131.9413820809748</v>
+        <v>131.5051931010875</v>
       </c>
       <c r="V24" t="n">
-        <v>138.8005871494253</v>
+        <v>138.364398169538</v>
       </c>
       <c r="W24" t="n">
-        <v>157.6949831609196</v>
+        <v>157.2587941810323</v>
       </c>
       <c r="X24" t="n">
-        <v>111.7729852034775</v>
+        <v>111.3367962235902</v>
       </c>
       <c r="Y24" t="n">
-        <v>111.6826957773044</v>
+        <v>111.2465067974171</v>
       </c>
     </row>
     <row r="25">
@@ -24321,28 +24321,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85.8319801819373</v>
+        <v>85.39579120204999</v>
       </c>
       <c r="C25" t="n">
-        <v>73.24682109862783</v>
+        <v>72.81063211874053</v>
       </c>
       <c r="D25" t="n">
-        <v>54.61547301821236</v>
+        <v>54.17928403832505</v>
       </c>
       <c r="E25" t="n">
-        <v>52.43396264656917</v>
+        <v>51.99777366668187</v>
       </c>
       <c r="F25" t="n">
-        <v>51.42104802293125</v>
+        <v>50.98485904304394</v>
       </c>
       <c r="G25" t="n">
-        <v>73.99097935845876</v>
+        <v>73.55479037857145</v>
       </c>
       <c r="H25" t="n">
-        <v>68.22717250743958</v>
+        <v>67.79098352755227</v>
       </c>
       <c r="I25" t="n">
-        <v>61.45047492725828</v>
+        <v>61.01428594737098</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>83.29339137716948</v>
+        <v>82.85720239728218</v>
       </c>
       <c r="S25" t="n">
-        <v>130.0165980369723</v>
+        <v>129.5804090570849</v>
       </c>
       <c r="T25" t="n">
-        <v>133.9455894282815</v>
+        <v>133.5094004483942</v>
       </c>
       <c r="U25" t="n">
-        <v>192.3190293564909</v>
+        <v>191.8828403766036</v>
       </c>
       <c r="V25" t="n">
-        <v>158.137643323828</v>
+        <v>157.7014543439407</v>
       </c>
       <c r="W25" t="n">
-        <v>192.522998336591</v>
+        <v>192.0868093567037</v>
       </c>
       <c r="X25" t="n">
-        <v>131.7096553890372</v>
+        <v>131.2734664091498</v>
       </c>
       <c r="Y25" t="n">
-        <v>124.5846533520948</v>
+        <v>124.1484643722075</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>292.7338416634806</v>
+        <v>293.3372088120655</v>
       </c>
       <c r="C26" t="n">
-        <v>275.2728917710076</v>
+        <v>275.8762589195925</v>
       </c>
       <c r="D26" t="n">
-        <v>264.683041620683</v>
+        <v>265.2864087692679</v>
       </c>
       <c r="E26" t="n">
-        <v>291.9303700722618</v>
+        <v>292.5337372208467</v>
       </c>
       <c r="F26" t="n">
-        <v>316.8760457417114</v>
+        <v>317.4794128902964</v>
       </c>
       <c r="G26" t="n">
-        <v>325.302737515135</v>
+        <v>325.90610466372</v>
       </c>
       <c r="H26" t="n">
-        <v>249.4748021157671</v>
+        <v>250.0781692643521</v>
       </c>
       <c r="I26" t="n">
-        <v>120.4758895704059</v>
+        <v>121.0792567189908</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>59.86911794114968</v>
+        <v>60.4724850897346</v>
       </c>
       <c r="S26" t="n">
-        <v>119.0200695862453</v>
+        <v>119.6234367348303</v>
       </c>
       <c r="T26" t="n">
-        <v>133.0958495641314</v>
+        <v>133.6992167127163</v>
       </c>
       <c r="U26" t="n">
-        <v>161.3456529078365</v>
+        <v>161.9490200564214</v>
       </c>
       <c r="V26" t="n">
-        <v>237.7522584701349</v>
+        <v>238.3556256187198</v>
       </c>
       <c r="W26" t="n">
-        <v>259.240968717413</v>
+        <v>259.8443358659979</v>
       </c>
       <c r="X26" t="n">
-        <v>279.731100678469</v>
+        <v>280.334467827054</v>
       </c>
       <c r="Y26" t="n">
-        <v>296.2379386560536</v>
+        <v>296.8413058046385</v>
       </c>
     </row>
     <row r="27">
@@ -24479,25 +24479,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>76.53318364986734</v>
+        <v>77.13655079845226</v>
       </c>
       <c r="C27" t="n">
-        <v>82.70849898831574</v>
+        <v>83.31186613690066</v>
       </c>
       <c r="D27" t="n">
-        <v>57.44506556463875</v>
+        <v>58.04843271322368</v>
       </c>
       <c r="E27" t="n">
-        <v>67.64508045540094</v>
+        <v>68.24844760398587</v>
       </c>
       <c r="F27" t="n">
-        <v>55.06921239338388</v>
+        <v>55.6725795419688</v>
       </c>
       <c r="G27" t="n">
-        <v>47.34351716321063</v>
+        <v>47.94688431179556</v>
       </c>
       <c r="H27" t="n">
-        <v>22.23544423649646</v>
+        <v>22.83881138508139</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>10.15783415264313</v>
+        <v>10.76120130122806</v>
       </c>
       <c r="S27" t="n">
-        <v>81.68317110383782</v>
+        <v>82.28653825242274</v>
       </c>
       <c r="T27" t="n">
-        <v>110.1647286948216</v>
+        <v>110.7680958434065</v>
       </c>
       <c r="U27" t="n">
-        <v>135.9413820809748</v>
+        <v>136.5447492295597</v>
       </c>
       <c r="V27" t="n">
-        <v>142.8005871494253</v>
+        <v>143.4039542980102</v>
       </c>
       <c r="W27" t="n">
-        <v>161.6949831609196</v>
+        <v>162.2983503095045</v>
       </c>
       <c r="X27" t="n">
-        <v>115.7729852034775</v>
+        <v>116.3763523520624</v>
       </c>
       <c r="Y27" t="n">
-        <v>115.6826957773044</v>
+        <v>116.2860629258893</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>89.8319801819373</v>
+        <v>90.43534733052222</v>
       </c>
       <c r="C28" t="n">
-        <v>77.24682109862783</v>
+        <v>77.85018824721276</v>
       </c>
       <c r="D28" t="n">
-        <v>58.61547301821236</v>
+        <v>59.21884016679728</v>
       </c>
       <c r="E28" t="n">
-        <v>56.43396264656917</v>
+        <v>57.03732979515409</v>
       </c>
       <c r="F28" t="n">
-        <v>55.42104802293125</v>
+        <v>56.02441517151617</v>
       </c>
       <c r="G28" t="n">
-        <v>77.99097935845876</v>
+        <v>78.59434650704368</v>
       </c>
       <c r="H28" t="n">
-        <v>72.22717250743958</v>
+        <v>72.8305396560245</v>
       </c>
       <c r="I28" t="n">
-        <v>65.45047492725828</v>
+        <v>66.05384207584321</v>
       </c>
       <c r="J28" t="n">
-        <v>3.359180116672775</v>
+        <v>3.962547265257697</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>87.29339137716948</v>
+        <v>87.89675852575441</v>
       </c>
       <c r="S28" t="n">
-        <v>134.0165980369723</v>
+        <v>134.6199651855572</v>
       </c>
       <c r="T28" t="n">
-        <v>137.9455894282815</v>
+        <v>138.5489565768664</v>
       </c>
       <c r="U28" t="n">
-        <v>196.3190293564909</v>
+        <v>196.9223965050758</v>
       </c>
       <c r="V28" t="n">
-        <v>162.137643323828</v>
+        <v>162.7410104724129</v>
       </c>
       <c r="W28" t="n">
-        <v>196.522998336591</v>
+        <v>197.1263654851759</v>
       </c>
       <c r="X28" t="n">
-        <v>135.7096553890372</v>
+        <v>136.3130225376221</v>
       </c>
       <c r="Y28" t="n">
-        <v>128.5846533520948</v>
+        <v>129.1880205006797</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C29" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D29" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E29" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F29" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G29" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H29" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I29" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719525</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793902</v>
       </c>
       <c r="S29" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303468</v>
       </c>
       <c r="T29" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092069</v>
       </c>
       <c r="U29" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446258</v>
       </c>
       <c r="V29" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069242</v>
       </c>
       <c r="W29" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542023</v>
       </c>
       <c r="X29" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y29" t="n">
-        <v>248.2379386560536</v>
+        <v>248.8944214928429</v>
       </c>
     </row>
     <row r="30">
@@ -24716,19 +24716,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665668</v>
       </c>
       <c r="C30" t="n">
-        <v>34.70849898831574</v>
+        <v>35.36498182510508</v>
       </c>
       <c r="D30" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142809</v>
       </c>
       <c r="E30" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219028</v>
       </c>
       <c r="F30" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173216</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062716</v>
       </c>
       <c r="T30" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161094</v>
       </c>
       <c r="U30" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776416</v>
       </c>
       <c r="V30" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621461</v>
       </c>
       <c r="W30" t="n">
-        <v>113.6949831609196</v>
+        <v>114.3514659977089</v>
       </c>
       <c r="X30" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026681</v>
       </c>
       <c r="Y30" t="n">
-        <v>67.68269577730436</v>
+        <v>68.3391786140937</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872663</v>
       </c>
       <c r="C31" t="n">
-        <v>29.24682109862783</v>
+        <v>29.90330393541717</v>
       </c>
       <c r="D31" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500169</v>
       </c>
       <c r="E31" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358508</v>
       </c>
       <c r="F31" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720582</v>
       </c>
       <c r="G31" t="n">
-        <v>29.99097935845876</v>
+        <v>30.6474621952481</v>
       </c>
       <c r="H31" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422891</v>
       </c>
       <c r="I31" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404762</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395882</v>
       </c>
       <c r="S31" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376159</v>
       </c>
       <c r="T31" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507083</v>
       </c>
       <c r="U31" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932802</v>
       </c>
       <c r="V31" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606173</v>
       </c>
       <c r="W31" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733803</v>
       </c>
       <c r="X31" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582649</v>
       </c>
       <c r="Y31" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888413</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C32" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D32" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E32" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F32" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G32" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H32" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I32" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S32" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T32" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U32" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V32" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W32" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X32" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y32" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="33">
@@ -24953,19 +24953,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C33" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D33" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E33" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F33" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T33" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U33" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V33" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W33" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X33" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y33" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C34" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D34" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E34" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F34" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G34" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H34" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I34" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S34" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T34" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U34" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V34" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W34" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X34" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y34" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C35" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D35" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E35" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F35" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G35" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H35" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I35" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S35" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T35" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U35" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V35" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W35" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X35" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y35" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C36" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D36" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E36" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F36" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T36" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U36" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V36" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W36" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X36" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y36" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C37" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D37" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E37" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F37" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G37" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H37" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I37" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S37" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T37" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U37" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V37" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W37" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X37" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y37" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C38" t="n">
-        <v>227.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D38" t="n">
-        <v>216.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E38" t="n">
-        <v>243.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F38" t="n">
-        <v>268.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G38" t="n">
-        <v>277.302737515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H38" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I38" t="n">
-        <v>72.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S38" t="n">
-        <v>71.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T38" t="n">
-        <v>85.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U38" t="n">
-        <v>113.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V38" t="n">
-        <v>189.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W38" t="n">
-        <v>211.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X38" t="n">
-        <v>231.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y38" t="n">
-        <v>248.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="39">
@@ -25427,19 +25427,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C39" t="n">
-        <v>34.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D39" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E39" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F39" t="n">
-        <v>7.069212393383879</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T39" t="n">
-        <v>62.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U39" t="n">
-        <v>87.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V39" t="n">
-        <v>94.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W39" t="n">
-        <v>113.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X39" t="n">
-        <v>67.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y39" t="n">
-        <v>67.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>41.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C40" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D40" t="n">
-        <v>10.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E40" t="n">
-        <v>8.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F40" t="n">
-        <v>7.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G40" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H40" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I40" t="n">
-        <v>17.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>39.29339137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S40" t="n">
-        <v>86.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T40" t="n">
-        <v>89.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U40" t="n">
-        <v>148.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V40" t="n">
-        <v>114.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W40" t="n">
-        <v>148.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X40" t="n">
-        <v>87.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y40" t="n">
-        <v>80.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>262.7338416634806</v>
+        <v>262.6202601976805</v>
       </c>
       <c r="C41" t="n">
-        <v>245.2728917710076</v>
+        <v>245.1593103052075</v>
       </c>
       <c r="D41" t="n">
-        <v>234.683041620683</v>
+        <v>234.5694601548829</v>
       </c>
       <c r="E41" t="n">
-        <v>261.9303700722618</v>
+        <v>261.8167886064617</v>
       </c>
       <c r="F41" t="n">
-        <v>286.8760457417114</v>
+        <v>286.7624642759114</v>
       </c>
       <c r="G41" t="n">
-        <v>295.302737515135</v>
+        <v>295.189156049335</v>
       </c>
       <c r="H41" t="n">
-        <v>219.4748021157671</v>
+        <v>219.3612206499671</v>
       </c>
       <c r="I41" t="n">
-        <v>90.47588957040591</v>
+        <v>90.36230810460587</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>29.86911794114968</v>
+        <v>29.75553647534964</v>
       </c>
       <c r="S41" t="n">
-        <v>89.02006958624534</v>
+        <v>88.9064881204453</v>
       </c>
       <c r="T41" t="n">
-        <v>103.0958495641314</v>
+        <v>102.9822680983313</v>
       </c>
       <c r="U41" t="n">
-        <v>131.3456529078365</v>
+        <v>131.2320714420364</v>
       </c>
       <c r="V41" t="n">
-        <v>207.7522584701349</v>
+        <v>207.6386770043349</v>
       </c>
       <c r="W41" t="n">
-        <v>229.240968717413</v>
+        <v>229.127387251613</v>
       </c>
       <c r="X41" t="n">
-        <v>249.731100678469</v>
+        <v>249.617519212669</v>
       </c>
       <c r="Y41" t="n">
-        <v>266.2379386560536</v>
+        <v>266.1243571902535</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>46.53318364986734</v>
+        <v>46.4196021840673</v>
       </c>
       <c r="C42" t="n">
-        <v>52.70849898831574</v>
+        <v>52.5949175225157</v>
       </c>
       <c r="D42" t="n">
-        <v>27.44506556463875</v>
+        <v>27.33148409883871</v>
       </c>
       <c r="E42" t="n">
-        <v>37.64508045540094</v>
+        <v>37.53149898960091</v>
       </c>
       <c r="F42" t="n">
-        <v>25.06921239338388</v>
+        <v>24.95563092758384</v>
       </c>
       <c r="G42" t="n">
-        <v>17.34351716321063</v>
+        <v>17.2299356974106</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>51.68317110383782</v>
+        <v>51.56958963803778</v>
       </c>
       <c r="T42" t="n">
-        <v>80.1647286948216</v>
+        <v>80.05114722902157</v>
       </c>
       <c r="U42" t="n">
-        <v>105.9413820809748</v>
+        <v>105.8278006151748</v>
       </c>
       <c r="V42" t="n">
-        <v>112.8005871494253</v>
+        <v>112.6870056836252</v>
       </c>
       <c r="W42" t="n">
-        <v>131.6949831609196</v>
+        <v>131.5814016951196</v>
       </c>
       <c r="X42" t="n">
-        <v>85.77298520347748</v>
+        <v>85.65940373767744</v>
       </c>
       <c r="Y42" t="n">
-        <v>85.68269577730436</v>
+        <v>85.56911431150432</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>59.8319801819373</v>
+        <v>59.71839871613726</v>
       </c>
       <c r="C43" t="n">
-        <v>47.24682109862783</v>
+        <v>47.1332396328278</v>
       </c>
       <c r="D43" t="n">
-        <v>28.61547301821236</v>
+        <v>28.50189155241232</v>
       </c>
       <c r="E43" t="n">
-        <v>26.43396264656917</v>
+        <v>26.32038118076913</v>
       </c>
       <c r="F43" t="n">
-        <v>25.42104802293125</v>
+        <v>25.30746655713121</v>
       </c>
       <c r="G43" t="n">
-        <v>47.99097935845876</v>
+        <v>47.87739789265872</v>
       </c>
       <c r="H43" t="n">
-        <v>42.22717250743958</v>
+        <v>42.11359104163954</v>
       </c>
       <c r="I43" t="n">
-        <v>35.45047492725828</v>
+        <v>35.33689346145825</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>57.29339137716948</v>
+        <v>57.17980991136945</v>
       </c>
       <c r="S43" t="n">
-        <v>104.0165980369723</v>
+        <v>103.9030165711722</v>
       </c>
       <c r="T43" t="n">
-        <v>107.9455894282815</v>
+        <v>107.8320079624815</v>
       </c>
       <c r="U43" t="n">
-        <v>166.3190293564909</v>
+        <v>166.2054478906908</v>
       </c>
       <c r="V43" t="n">
-        <v>132.137643323828</v>
+        <v>132.0240618580279</v>
       </c>
       <c r="W43" t="n">
-        <v>166.522998336591</v>
+        <v>166.4094168707909</v>
       </c>
       <c r="X43" t="n">
-        <v>105.7096553890372</v>
+        <v>105.5960739232371</v>
       </c>
       <c r="Y43" t="n">
-        <v>98.58465335209479</v>
+        <v>98.47107188629475</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>329394.5107789515</v>
+        <v>329776.8765611869</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>428635.7080755992</v>
+        <v>429185.9779212861</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428635.7080755992</v>
+        <v>429185.9779212861</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>428635.7080755992</v>
+        <v>429185.9779212861</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>428635.7080755992</v>
+        <v>429185.9779212861</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>423478.6951317489</v>
+        <v>422697.6122232195</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>480396.9232563012</v>
+        <v>479683.5627465326</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>480396.9232563012</v>
+        <v>479683.5627465326</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>480396.9232563012</v>
+        <v>479683.5627465326</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>480396.9232563012</v>
+        <v>479683.5627465326</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>459826.276205686</v>
+        <v>459956.3201691388</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>860240.1556528903</v>
+      </c>
+      <c r="C2" t="n">
+        <v>860240.15565289</v>
+      </c>
+      <c r="D2" t="n">
         <v>860240.1556528902</v>
       </c>
-      <c r="C2" t="n">
-        <v>860240.1556528902</v>
-      </c>
-      <c r="D2" t="n">
-        <v>860240.1556528903</v>
-      </c>
       <c r="E2" t="n">
-        <v>283325.9144130173</v>
+        <v>284007.2975455795</v>
       </c>
       <c r="F2" t="n">
-        <v>463144.4985304574</v>
+        <v>464194.9637269404</v>
       </c>
       <c r="G2" t="n">
-        <v>463144.4985304573</v>
+        <v>464194.9637269404</v>
       </c>
       <c r="H2" t="n">
-        <v>463144.4985304573</v>
+        <v>464194.9637269404</v>
       </c>
       <c r="I2" t="n">
-        <v>463144.4985304573</v>
+        <v>464194.9637269404</v>
       </c>
       <c r="J2" t="n">
-        <v>453426.7271915172</v>
+        <v>451958.4453027787</v>
       </c>
       <c r="K2" t="n">
-        <v>566247.820668448</v>
+        <v>564754.5060299464</v>
       </c>
       <c r="L2" t="n">
-        <v>566247.8206684478</v>
+        <v>564754.5060299466</v>
       </c>
       <c r="M2" t="n">
-        <v>566247.8206684475</v>
+        <v>564754.5060299465</v>
       </c>
       <c r="N2" t="n">
-        <v>566247.8206684476</v>
+        <v>564754.5060299464</v>
       </c>
       <c r="O2" t="n">
-        <v>524530.7272843419</v>
+        <v>524794.1499630841</v>
       </c>
       <c r="P2" t="n">
         <v>225765.5516160374</v>
@@ -26322,10 +26322,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>17600</v>
+        <v>17815.59346070626</v>
       </c>
       <c r="F3" t="n">
-        <v>57600</v>
+        <v>57733.35772320356</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -26337,10 +26337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14400</v>
+        <v>13783.94855792848</v>
       </c>
       <c r="K3" t="n">
-        <v>96000</v>
+        <v>96090.86517264003</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26374,40 +26374,40 @@
         <v>467615.9599317312</v>
       </c>
       <c r="E4" t="n">
-        <v>175333.232747354</v>
+        <v>175685.5478003903</v>
       </c>
       <c r="F4" t="n">
-        <v>269948.8600633092</v>
+        <v>270491.0025380308</v>
       </c>
       <c r="G4" t="n">
-        <v>269948.8600633093</v>
+        <v>270491.0025380309</v>
       </c>
       <c r="H4" t="n">
-        <v>269948.8600633092</v>
+        <v>270491.0025380308</v>
       </c>
       <c r="I4" t="n">
-        <v>269948.8600633092</v>
+        <v>270491.0025380307</v>
       </c>
       <c r="J4" t="n">
-        <v>264866.9207701758</v>
+        <v>264092.5943250212</v>
       </c>
       <c r="K4" t="n">
-        <v>323418.9103148851</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="L4" t="n">
-        <v>323418.9103148851</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="M4" t="n">
-        <v>323418.9103148851</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="N4" t="n">
-        <v>323418.9103148851</v>
+        <v>322644.7142125412</v>
       </c>
       <c r="O4" t="n">
-        <v>301840.7065168585</v>
+        <v>301971.3657489925</v>
       </c>
       <c r="P4" t="n">
-        <v>144745.8284464477</v>
+        <v>144738.4206832074</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1849.518</v>
+        <v>1872.173908310146</v>
       </c>
       <c r="F5" t="n">
-        <v>7902.486</v>
+        <v>7939.155971350147</v>
       </c>
       <c r="G5" t="n">
-        <v>7902.486</v>
+        <v>7939.155971350147</v>
       </c>
       <c r="H5" t="n">
-        <v>7902.486</v>
+        <v>7939.155971350147</v>
       </c>
       <c r="I5" t="n">
-        <v>7902.486</v>
+        <v>7939.155971350147</v>
       </c>
       <c r="J5" t="n">
-        <v>7566.21</v>
+        <v>7515.485527185614</v>
       </c>
       <c r="K5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439396</v>
       </c>
       <c r="L5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="M5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="N5" t="n">
-        <v>11601.522</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="O5" t="n">
-        <v>10088.28</v>
+        <v>10097.82868024834</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>358996.5957211591</v>
+      </c>
+      <c r="C6" t="n">
+        <v>358996.5957211588</v>
+      </c>
+      <c r="D6" t="n">
         <v>358996.595721159</v>
       </c>
-      <c r="C6" t="n">
-        <v>358996.595721159</v>
-      </c>
-      <c r="D6" t="n">
-        <v>358996.5957211591</v>
-      </c>
       <c r="E6" t="n">
-        <v>88543.16366566326</v>
+        <v>88633.9823761728</v>
       </c>
       <c r="F6" t="n">
-        <v>127693.1524671482</v>
+        <v>128031.4474943559</v>
       </c>
       <c r="G6" t="n">
-        <v>185293.152467148</v>
+        <v>185764.8052175594</v>
       </c>
       <c r="H6" t="n">
-        <v>185293.1524671481</v>
+        <v>185764.8052175594</v>
       </c>
       <c r="I6" t="n">
-        <v>185293.1524671481</v>
+        <v>185764.8052175596</v>
       </c>
       <c r="J6" t="n">
-        <v>166593.5964213414</v>
+        <v>166566.4168926434</v>
       </c>
       <c r="K6" t="n">
-        <v>135227.3883535629</v>
+        <v>134472.5945003712</v>
       </c>
       <c r="L6" t="n">
-        <v>231227.3883535626</v>
+        <v>230563.4596730115</v>
       </c>
       <c r="M6" t="n">
-        <v>231227.3883535624</v>
+        <v>230563.4596730114</v>
       </c>
       <c r="N6" t="n">
-        <v>231227.3883535625</v>
+        <v>230563.4596730112</v>
       </c>
       <c r="O6" t="n">
-        <v>212601.7407674834</v>
+        <v>212724.9555338433</v>
       </c>
       <c r="P6" t="n">
-        <v>81019.72316958965</v>
+        <v>81027.13093283001</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J2" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K2" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="L2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="N2" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="O2" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,10 +26849,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>22.26949182588282</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>72.16669715400445</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -26861,28 +26861,28 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>17.2299356974106</v>
       </c>
       <c r="K2" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26947,13 +26947,13 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -26965,28 +26965,28 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>22.26949182588282</v>
       </c>
       <c r="K2" t="n">
-        <v>72</v>
+        <v>72.16669715400445</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>18</v>
+        <v>17.2299356974106</v>
       </c>
       <c r="P2" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
     </row>
     <row r="3">
@@ -28012,31 +28012,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="H11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>19.13609599108519</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28057,31 +28057,31 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="R11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="T11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="U11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="V11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="W11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="Y11" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
     </row>
     <row r="12">
@@ -28091,43 +28091,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="E12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="G12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="M12" t="n">
-        <v>16.18867924528302</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="S12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="T12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="U12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="V12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="W12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="Y12" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
     </row>
     <row r="13">
@@ -28170,76 +28170,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="G13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="H13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="M13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="O13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="R13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="T13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="V13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="W13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>22.26949182588285</v>
       </c>
     </row>
     <row r="14">
@@ -28249,31 +28249,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -28294,31 +28294,31 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y14" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="15">
@@ -28328,31 +28328,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J15" t="n">
-        <v>73.77317846933916</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -28361,43 +28361,43 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="P15" t="n">
-        <v>94</v>
+        <v>69.49078057010665</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y15" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="16">
@@ -28407,76 +28407,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="L16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="M16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="N16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="O16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="P16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Q16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y16" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="17">
@@ -28486,31 +28486,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -28531,31 +28531,31 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y17" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="18">
@@ -28565,34 +28565,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>69.49078057010611</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -28601,40 +28601,40 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>69.16981132075472</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Q18" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y18" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="19">
@@ -28644,76 +28644,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="L19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="M19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="N19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="O19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="P19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Q19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y19" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="20">
@@ -28723,31 +28723,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -28768,31 +28768,31 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y20" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="21">
@@ -28802,31 +28802,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I21" t="n">
-        <v>94</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -28835,43 +28835,43 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="O21" t="n">
-        <v>69.16981132075472</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y21" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="22">
@@ -28881,76 +28881,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="L22" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="P22" t="n">
-        <v>94</v>
+        <v>8.903215826969275</v>
       </c>
       <c r="Q22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y22" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="23">
@@ -28960,31 +28960,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -29005,31 +29005,31 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>80.77386934673366</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y23" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="24">
@@ -29039,34 +29039,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29075,40 +29075,40 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="R24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="25">
@@ -29118,76 +29118,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="C25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="E25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="F25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="G25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="H25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="J25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="K25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="L25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="M25" t="n">
-        <v>94</v>
+        <v>77.95378321100242</v>
       </c>
       <c r="N25" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="P25" t="n">
-        <v>94</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>94</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="S25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="T25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="U25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="V25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="W25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="X25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
       <c r="Y25" t="n">
-        <v>94</v>
+        <v>94.43618897988731</v>
       </c>
     </row>
     <row r="26">
@@ -29197,31 +29197,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J26" t="n">
-        <v>90</v>
+        <v>76.81821214870462</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -29242,31 +29242,31 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>77.65807496356784</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y26" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="27">
@@ -29276,37 +29276,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="L27" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -29318,34 +29318,34 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y27" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="28">
@@ -29355,76 +29355,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="C28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="D28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="E28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="F28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="G28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="H28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="I28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="K28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="L28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="M28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="N28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="O28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="P28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Q28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="R28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="S28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="T28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="U28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="V28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="W28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="X28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="Y28" t="n">
-        <v>90</v>
+        <v>89.39663285141508</v>
       </c>
     </row>
     <row r="29">
@@ -29434,31 +29434,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="C29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="D29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="E29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="F29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="G29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="H29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="I29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="J29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -29479,31 +29479,31 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="R29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="S29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="T29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="U29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="V29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="W29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="X29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="Y29" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
     </row>
     <row r="30">
@@ -29513,76 +29513,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="C30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="D30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="E30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="F30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>99.52238000000006</v>
+        <v>99.52238</v>
       </c>
       <c r="J30" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="L30" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>138</v>
+        <v>133.5616913556508</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="R30" t="n">
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="T30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="U30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="V30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="W30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="X30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="Y30" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
     </row>
     <row r="31">
@@ -29592,76 +29592,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="C31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="D31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="E31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="F31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="G31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="H31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="I31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="J31" t="n">
-        <v>126.9954214393961</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
-        <v>118.748657055937</v>
+        <v>129.0132581705354</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>137.7280040491476</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="Q31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="R31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="S31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="T31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="U31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="V31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="W31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="X31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
       <c r="Y31" t="n">
-        <v>138</v>
+        <v>137.3435171632107</v>
       </c>
     </row>
     <row r="32">
@@ -29671,31 +29671,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -29716,31 +29716,31 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y32" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="33">
@@ -29750,37 +29750,37 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632107</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>99.52238000000006</v>
+        <v>99.52238</v>
       </c>
       <c r="J33" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -29789,37 +29789,37 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>138</v>
+        <v>90.00955927944929</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y33" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J34" t="n">
         <v>126.9954214393961</v>
@@ -29871,34 +29871,34 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>137.7280040491476</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q34" t="n">
-        <v>134.8472791200853</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y34" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="35">
@@ -29908,31 +29908,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -29953,31 +29953,31 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y35" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="36">
@@ -29987,76 +29987,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>99.52238</v>
       </c>
       <c r="J36" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L36" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>12.26794579084032</v>
       </c>
       <c r="N36" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R36" t="n">
-        <v>104.4734297269266</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y36" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J37" t="n">
         <v>126.9954214393961</v>
@@ -30105,37 +30105,37 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="P37" t="n">
-        <v>137.7280040491476</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y37" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="38">
@@ -30145,31 +30145,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -30190,31 +30190,31 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y38" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="39">
@@ -30224,76 +30224,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
-        <v>99.52238000000006</v>
+        <v>99.52238</v>
       </c>
       <c r="J39" t="n">
         <v>126.8376266666667</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>17.02885226536359</v>
       </c>
       <c r="L39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
-        <v>129.5571530947016</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y39" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J40" t="n">
         <v>126.9954214393961</v>
@@ -30333,7 +30333,7 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -30345,34 +30345,34 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>137.7280040491476</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Q40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="R40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y40" t="n">
-        <v>138</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="41">
@@ -30382,31 +30382,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="C41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="D41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="E41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="F41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="G41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="H41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="I41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="J41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -30427,31 +30427,31 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>87.0867809472423</v>
+        <v>120.1135814658</v>
       </c>
       <c r="R41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="S41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="T41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="U41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="V41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="W41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="X41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="Y41" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
     </row>
     <row r="42">
@@ -30461,76 +30461,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="C42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="D42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="E42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="F42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="G42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364966</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>99.52238</v>
       </c>
       <c r="J42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="K42" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>120.1135814658</v>
       </c>
       <c r="M42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="N42" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>120.1135814658</v>
       </c>
       <c r="P42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="Q42" t="n">
-        <v>120</v>
+        <v>28.46933869510694</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>120.1135814658</v>
       </c>
       <c r="S42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="T42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="U42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="V42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="W42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="X42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="Y42" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
     </row>
     <row r="43">
@@ -30540,34 +30540,34 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="C43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="D43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="E43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="F43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="G43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="H43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="I43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="J43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="K43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -30582,34 +30582,34 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="Q43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="R43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="S43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="T43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="U43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="V43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="W43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="X43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
       <c r="Y43" t="n">
-        <v>120</v>
+        <v>120.1135814658</v>
       </c>
     </row>
     <row r="44">
